--- a/光伏配储项目/电价数据/2026/岗华站.xlsx
+++ b/光伏配储项目/电价数据/2026/岗华站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.34279</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.80049</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.27636</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07934000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.39374</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.7133</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17714</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.27722</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25839</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26295</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24769</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.18771</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.6116900000000001</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.40268</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.4152</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.60941</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5910299999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7594</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.14653</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39769</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.72291</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43667</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44388</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.67706</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.90971</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.54891</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.22143</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.41478</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.09273</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.10321</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.32962</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.41149</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.46738</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.72827</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.78261</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.27021</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.85082</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.88378</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8000700000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7515700000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.50496</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47294</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46341</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41262</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42247</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.72861</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76851</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.90947</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.91964</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5031100000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51854</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.51052</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51088</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49312</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40334</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47447</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.26451</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.39077</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.4904</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.5328200000000001</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.53455</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.69329</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.65526</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.90698</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.38068</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.58782</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.78218</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5440199999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.45359</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.38587</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.41885</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.71504</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.41105</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.38804</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.1239</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.65971</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.9215800000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.05895</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.32398</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.20141</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.96841</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.32355</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.18333</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.3834</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.06984</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.16795</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7817999999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.07364</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.99529</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.03448</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.90322</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.14136</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.97163</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.47101</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.9086799999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9321499999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.46888</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.44457</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.46266</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33501</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.52235</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.5000599999999999</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.50102</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44978</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41733</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43277</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44902</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39456</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.4791</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44729</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4428</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.14643</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.18495</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27528</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.39498</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.10495</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.9410299999999999</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.7535299999999999</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.73948</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.95723</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.95196</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.95862</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.94123</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.56092</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.86176</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.84912</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.84905</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.06177</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5809099999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.65464</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.90525</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.8962</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.74036</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.80301</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5535399999999999</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.98181</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.5314099999999999</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.4569</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5169900000000001</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5330199999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.6479</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.6980499999999999</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.68114</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.66943</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.62454</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6995399999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.48642</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5164800000000001</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.66442</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.8600099999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.8023400000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.06115</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.47938</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.66476</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.47782</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5885900000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.72187</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.9145800000000001</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.6339199999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.09122</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.8195399999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.58008</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.7194199999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4527</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.47508</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40715</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34259</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5162899999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49626</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44128</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39179</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45016</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40472</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44717</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44049</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.52749</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.73946</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.46945</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46072</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.73158</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.4191</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.39382</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.45389</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.74478</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.6072799999999999</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.48468</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.43833</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.55675</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.62463</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.6307200000000001</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.6241599999999999</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45068</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.51673</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.5482899999999999</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.6497999999999999</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.79827</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.57164</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.65987</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.60975</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.5813700000000001</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50262</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.51095</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.48158</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.46792</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.45849</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.40133</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.37069</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37565</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28795</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14311</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40992</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.44647</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26927</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25869</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24325</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10868</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.29882</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.04013000000000001</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26342</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.45119</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42238</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31606</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.41977</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.23381</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.24116</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.25666</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28537</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.18664</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.18117</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.2451</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.19275</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24542</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21075</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.18825</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.16906</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24608</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.26785</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.19638</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26544</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.09576999999999999</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.03929</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.009869999999999999</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20593</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04913</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27501</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19505</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.00821</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06007</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05828</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31509</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.43686</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.42796</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4452</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.48508</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.45307</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78811</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8702799999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6511399999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5712200000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45411</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42144</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39253</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38656</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44343</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.46153</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5878099999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6333099999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.9519299999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.5366799999999999</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.28503</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.4348399999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.70957</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.95165</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26469</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.40839</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.7220299999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.56768</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28411</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29411</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.17481</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26079</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26025</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27527</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.25939</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27956</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30202</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32252</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.8430800000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29141</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29606</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29121</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30307</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.5525099999999999</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.38586</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.56972</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.46774</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.46487</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.23375</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3952</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.39068</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.5086000000000001</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.58535</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.45835</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.42146</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.4414</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.43544</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.4521</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.57559</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.46675</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.43478</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.46429</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.46784</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.36509</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38177</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.50989</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.53823</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.35197</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.21403</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.69691</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.65119</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.95625</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.9444900000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.90818</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.54623</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.6019600000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.46092</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.40993</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.48286</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.44637</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.44363</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.48343</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43104</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3762</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.40995</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.4311</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.41764</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.54704</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.22297</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.42539</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.45887</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37723</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.28854</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.17238</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3757200000000001</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.41955</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.39404</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.37882</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.47823</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.56967</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.41519</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30316</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30898</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.1939</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.20967</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.1823</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.20441</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.17959</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.17196</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.26586</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.28954</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.22218</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.21707</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.39032</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.18033</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.26665</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.25374</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.20266</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29571</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.17839</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.23788</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.20556</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.24782</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28662</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26854</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28525</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.29345</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29045</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.28935</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27856</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.27815</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.30034</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.40441</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.41105</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39512</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28172</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24581</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.27896</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28773</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29309</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2817</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.2849100000000001</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28624</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28111</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28812</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28658</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28622</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.44541</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30227</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28452</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28407</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29155</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29357</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30413</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28581</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.40566</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.10181</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41801</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6698500000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38942</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.4937</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48601</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44044</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.50156</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.43239</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.55875</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27636</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.43602</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.27326</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.42458</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.7583200000000001</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.54444</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.44793</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.43826</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41672</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.54622</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.42025</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.43276</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.46251</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.4578</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.37181</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.49667</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.42365</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.84414</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.48412</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42755</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.5582699999999999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.54448</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.79704</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.2795299999999999</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50485</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.42559</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.25094</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38304</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27738</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27815</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.27686</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.19289</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.18537</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27452</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27448</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27218</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.2745</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27194</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.18711</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.18451</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.14698</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23187</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28887</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29205</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.25969</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.18425</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.27231</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.19643</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.15955</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.15125</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.22409</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.24326</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.25921</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.40098</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33416</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.25501</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.27322</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.28836</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27033</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28241</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28535</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.23974</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.27047</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.20718</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.22986</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31924</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.27801</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.03135</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28669</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28294</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27115</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.27973</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29325</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28077</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28326</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27038</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28211</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28735</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28684</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27802</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27195</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.2814700000000001</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29096</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27171</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28259</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26892</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.28996</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30037</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6028300000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.5190900000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.19777</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29481</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28061</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30598</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30707</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40998</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44213</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49262</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.63319</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.59373</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.64005</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.78753</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48844</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40686</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.43926</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31244</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36359</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.28282</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.29951</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.27531</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.29103</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.28504</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44697</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40335</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41912</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.44655</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.48036</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.52019</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5729299999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40343</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.4267</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.41706</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.7085499999999999</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.83577</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39454</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.49964</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7063200000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.57131</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64134</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.30983</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40335</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39328</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.25867</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.28244</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.0178</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27182</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28073</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.27132</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.27861</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.28842</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.45348</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.45585</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.45792</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.47835</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.54801</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41498</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44345</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.44439</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.43618</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4865</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.43619</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36476</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.22281</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.25473</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.24695</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.23774</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.2806</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.20671</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.23975</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.27937</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.22111</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.15926</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.01927</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.26375</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.02153</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.02087</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.15951</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.03299000000000001</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.02094</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.14925</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.15361</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.18997</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.15135</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.15396</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.15658</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.02118</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.15919</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.02127</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.04743</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.16969</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.17623</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.14201</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28224</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.1897</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.25356</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.41887</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.00124</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.24575</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.2129</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.23975</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.26049</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.25764</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.19448</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.2005</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.26062</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.18608</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.29305</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.19852</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.28302</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22488</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.28407</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28092</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27011</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.02866</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.17864</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.17576</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26289</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.03739</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.19421</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.21633</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.2076</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.01092</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.03513</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.03514</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.0353</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.0353</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.03521</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.18877</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.0353</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.0353</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.16597</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.04995</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.0347</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.02837</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24239</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.01075</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.009089999999999999</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.20473</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02209</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.007940000000000001</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02937</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04342</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.01502</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.29145</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04921</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.0287</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.02563</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03203</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.23266</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.28424</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.03462</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27837</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30636</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28926</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28839</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.2634</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.02541</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.26786</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.27188</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27154</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.15542</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.15114</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15529</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.15284</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.14911</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.1387</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.03279</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.03207</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.03095</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41277</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.17819</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27048</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.22377</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.26459</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85578</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86268</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08802</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.03323</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24368</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28236</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28903</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.5806699999999999</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29522</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00193</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06958</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47553</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.61239</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.50369</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.74587</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9126000000000001</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.58399</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.41027</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.77867</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.7768999999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.78077</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.8710800000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3027</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.45767</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.28063</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.25959</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.25457</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.17612</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25238</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.24639</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24011</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.2058</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.23912</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.19139</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.15372</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.18716</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.14856</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.15109</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.14123</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.16758</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.2199</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.26552</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.23028</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.23884</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.24659</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27081</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.29227</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.27949</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25871</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39566</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.30329</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28537</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28651</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5572699999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.4542</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41899</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.4651</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.15661</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.7838999999999999</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.7831</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40557</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.41194</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.52708</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6510199999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8269</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40414</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.5364800000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42145</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19721</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.28834</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43457</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.4957</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.50173</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.01187</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.78146</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.53239</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.6756599999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46422</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49719</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6516799999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.6111799999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.9598099999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.79625</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.68798</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5689299999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31735</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28209</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.27922</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28659</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29699</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28404</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.27864</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.27554</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26293</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42331</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.53643</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19811</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43459</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.50371</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.44681</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.46738</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.6009500000000001</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.57337</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.63346</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.50093</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.42818</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.44689</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.53451</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.46177</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.4030899999999999</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.41339</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32104</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.67786</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39544</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.44434</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40865</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.26893</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.46213</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.67112</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.69453</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.5165599999999999</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.59112</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.7371799999999999</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.40137</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.40721</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.50648</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.5206799999999999</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.4969</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43831</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40531</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33556</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.44394</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17614</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1458</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19872</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14706</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28722</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04819</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12195</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22656</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26015</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14306</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14576</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28351</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.1872</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22691</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.18084</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.19305</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.22145</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.1878</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.40344</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.40296</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.6280800000000001</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.7141900000000001</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.5178400000000001</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>1.13797</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.56149</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.61522</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.44082</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.43696</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.49774</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.42289</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.69153</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.5642</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.6948200000000001</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.9795199999999999</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.73824</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.42407</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.67962</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.65189</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.67857</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.59011</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.44502</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.43386</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41857</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38861</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36635</v>
       </c>
     </row>
   </sheetData>
